--- a/data/modelos/traducao_ptbr.xlsx
+++ b/data/modelos/traducao_ptbr.xlsx
@@ -16363,7 +16363,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Jogador a tabela</t>
+          <t>Jogar a Tabela</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
